--- a/Dados-iniciais/sinan_agregado.xlsx
+++ b/Dados-iniciais/sinan_agregado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R646"/>
+  <dimension ref="A1:S646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>MG_60</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>TOTAL_AMPOLAS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -560,6 +565,9 @@
       <c r="R2" t="n">
         <v>1</v>
       </c>
+      <c r="S2" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -618,6 +626,9 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -676,6 +687,9 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -734,6 +748,9 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -791,6 +808,9 @@
       </c>
       <c r="R6" t="n">
         <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -850,6 +870,9 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -908,6 +931,9 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -966,6 +992,9 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1018,6 +1047,9 @@
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1070,6 +1102,9 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1128,6 +1163,9 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1186,6 +1224,9 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1244,6 +1285,9 @@
       <c r="R14" t="n">
         <v>1</v>
       </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1302,6 +1346,9 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1360,6 +1407,9 @@
       <c r="R16" t="n">
         <v>1</v>
       </c>
+      <c r="S16" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1418,6 +1468,9 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1474,6 +1527,9 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1516,6 +1572,9 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1574,6 +1633,9 @@
       <c r="R20" t="n">
         <v>4</v>
       </c>
+      <c r="S20" t="n">
+        <v>187</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1632,6 +1694,9 @@
       <c r="R21" t="n">
         <v>1</v>
       </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1690,6 +1755,9 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1748,6 +1816,9 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1800,6 +1871,9 @@
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1858,6 +1932,9 @@
       <c r="R25" t="n">
         <v>1</v>
       </c>
+      <c r="S25" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1916,6 +1993,9 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1974,6 +2054,9 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2032,6 +2115,9 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2090,6 +2176,9 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2147,6 +2236,9 @@
       </c>
       <c r="R30" t="n">
         <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -2188,6 +2280,9 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2246,6 +2341,9 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2304,6 +2402,9 @@
       <c r="R33" t="n">
         <v>56</v>
       </c>
+      <c r="S33" t="n">
+        <v>989</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2356,6 +2457,9 @@
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2414,6 +2518,9 @@
       <c r="R35" t="n">
         <v>1</v>
       </c>
+      <c r="S35" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2472,6 +2579,9 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2524,6 +2634,9 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2582,6 +2695,9 @@
       <c r="R38" t="n">
         <v>4</v>
       </c>
+      <c r="S38" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2640,6 +2756,9 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2698,6 +2817,9 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2755,6 +2877,9 @@
       </c>
       <c r="R41" t="n">
         <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -2800,6 +2925,9 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2848,6 +2976,9 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2906,6 +3037,9 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2962,6 +3096,9 @@
         <v>13</v>
       </c>
       <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3004,6 +3141,9 @@
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3062,6 +3202,9 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3120,6 +3263,9 @@
       <c r="R48" t="n">
         <v>8</v>
       </c>
+      <c r="S48" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3178,6 +3324,9 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3236,6 +3385,9 @@
       <c r="R50" t="n">
         <v>2</v>
       </c>
+      <c r="S50" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3294,6 +3446,9 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3352,6 +3507,9 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3410,6 +3568,9 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3468,6 +3629,9 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3526,6 +3690,9 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3584,6 +3751,9 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3641,6 +3811,9 @@
       </c>
       <c r="R57" t="n">
         <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -3670,6 +3843,7 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3728,6 +3902,9 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3786,6 +3963,9 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3843,6 +4023,9 @@
       </c>
       <c r="R61" t="n">
         <v>6</v>
+      </c>
+      <c r="S61" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="62">
@@ -3884,6 +4067,9 @@
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3912,6 +4098,7 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3970,6 +4157,9 @@
       <c r="R64" t="n">
         <v>2</v>
       </c>
+      <c r="S64" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4028,6 +4218,9 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4086,6 +4279,9 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4144,6 +4340,9 @@
       <c r="R67" t="n">
         <v>2</v>
       </c>
+      <c r="S67" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4202,6 +4401,9 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4260,6 +4462,9 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4318,6 +4523,9 @@
       <c r="R70" t="n">
         <v>2</v>
       </c>
+      <c r="S70" t="n">
+        <v>286</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4376,6 +4584,9 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4433,6 +4644,9 @@
       </c>
       <c r="R72" t="n">
         <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4480,6 +4694,9 @@
       <c r="R73" t="n">
         <v>1</v>
       </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4538,6 +4755,9 @@
       <c r="R74" t="n">
         <v>2</v>
       </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4595,6 +4815,9 @@
       </c>
       <c r="R75" t="n">
         <v>11</v>
+      </c>
+      <c r="S75" t="n">
+        <v>258</v>
       </c>
     </row>
     <row r="76">
@@ -4636,6 +4859,9 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4694,6 +4920,9 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4752,6 +4981,9 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4810,6 +5042,9 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4866,6 +5101,9 @@
         <v>16</v>
       </c>
       <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4914,6 +5152,9 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4954,6 +5195,9 @@
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4994,6 +5238,9 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5040,6 +5287,9 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5098,6 +5348,9 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5150,6 +5403,9 @@
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5208,6 +5464,9 @@
       <c r="R87" t="n">
         <v>2</v>
       </c>
+      <c r="S87" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5266,6 +5525,9 @@
       <c r="R88" t="n">
         <v>1</v>
       </c>
+      <c r="S88" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5324,6 +5586,9 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5382,6 +5647,9 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5440,6 +5708,9 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5498,6 +5769,9 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5556,6 +5830,9 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5614,6 +5891,9 @@
       <c r="R94" t="n">
         <v>2</v>
       </c>
+      <c r="S94" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5672,6 +5952,9 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5730,6 +6013,9 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5788,6 +6074,9 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5846,6 +6135,9 @@
       <c r="R98" t="n">
         <v>2</v>
       </c>
+      <c r="S98" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5903,6 +6195,9 @@
       </c>
       <c r="R99" t="n">
         <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="100">
@@ -5950,6 +6245,9 @@
       <c r="R100" t="n">
         <v>1</v>
       </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6008,6 +6306,9 @@
       <c r="R101" t="n">
         <v>3</v>
       </c>
+      <c r="S101" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6066,6 +6367,9 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6124,6 +6428,9 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6182,6 +6489,9 @@
       <c r="R104" t="n">
         <v>1</v>
       </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6240,6 +6550,9 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6292,6 +6605,9 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6350,6 +6666,9 @@
       <c r="R107" t="n">
         <v>1</v>
       </c>
+      <c r="S107" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6402,6 +6721,9 @@
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6442,6 +6764,9 @@
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6500,6 +6825,9 @@
       <c r="R110" t="n">
         <v>2</v>
       </c>
+      <c r="S110" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6558,6 +6886,9 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6610,6 +6941,9 @@
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
+      <c r="S112" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6667,6 +7001,9 @@
       </c>
       <c r="R113" t="n">
         <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -6696,6 +7033,7 @@
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6754,6 +7092,9 @@
       <c r="R115" t="n">
         <v>1</v>
       </c>
+      <c r="S115" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6812,6 +7153,9 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6870,6 +7214,9 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6928,6 +7275,9 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6974,6 +7324,9 @@
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
+      <c r="S119" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7026,6 +7379,9 @@
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
+      <c r="S120" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7084,6 +7440,9 @@
       <c r="R121" t="n">
         <v>1</v>
       </c>
+      <c r="S121" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7142,6 +7501,9 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7200,6 +7562,9 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7258,6 +7623,9 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7316,6 +7684,9 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7374,6 +7745,9 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7432,6 +7806,9 @@
       <c r="R127" t="n">
         <v>3</v>
       </c>
+      <c r="S127" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7490,6 +7867,9 @@
       <c r="R128" t="n">
         <v>2</v>
       </c>
+      <c r="S128" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7548,6 +7928,9 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7606,6 +7989,9 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7664,6 +8050,9 @@
       <c r="R131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7720,6 +8109,9 @@
         <v>15</v>
       </c>
       <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7762,6 +8154,9 @@
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7820,6 +8215,9 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
+      <c r="S134" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7878,6 +8276,9 @@
       <c r="R135" t="n">
         <v>2</v>
       </c>
+      <c r="S135" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7936,6 +8337,9 @@
       <c r="R136" t="n">
         <v>1</v>
       </c>
+      <c r="S136" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7993,6 +8397,9 @@
       </c>
       <c r="R137" t="n">
         <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="138">
@@ -8040,6 +8447,9 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8098,6 +8508,9 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8156,6 +8569,9 @@
       <c r="R140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8213,6 +8629,9 @@
       </c>
       <c r="R141" t="n">
         <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -8242,6 +8661,7 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8300,6 +8720,9 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8358,6 +8781,9 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8416,6 +8842,9 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8468,6 +8897,9 @@
       </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8526,6 +8958,9 @@
       <c r="R147" t="n">
         <v>0</v>
       </c>
+      <c r="S147" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8582,6 +9017,9 @@
         <v>4</v>
       </c>
       <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8630,6 +9068,9 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8687,6 +9128,9 @@
       </c>
       <c r="R150" t="n">
         <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="151">
@@ -8728,6 +9172,9 @@
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8786,6 +9233,9 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8844,6 +9294,9 @@
       <c r="R153" t="n">
         <v>0</v>
       </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8902,6 +9355,9 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8958,6 +9414,9 @@
         <v>3</v>
       </c>
       <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9000,6 +9459,9 @@
       </c>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
+      <c r="S156" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9058,6 +9520,9 @@
       <c r="R157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9115,6 +9580,9 @@
       </c>
       <c r="R158" t="n">
         <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="159">
@@ -9162,6 +9630,9 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9220,6 +9691,9 @@
       <c r="R160" t="n">
         <v>0</v>
       </c>
+      <c r="S160" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9278,6 +9752,9 @@
       <c r="R161" t="n">
         <v>3</v>
       </c>
+      <c r="S161" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9336,6 +9813,9 @@
       <c r="R162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9394,6 +9874,9 @@
       <c r="R163" t="n">
         <v>0</v>
       </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9450,6 +9933,9 @@
         <v>1</v>
       </c>
       <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9498,6 +9984,9 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
+      <c r="S165" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9556,6 +10045,9 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9614,6 +10106,9 @@
       <c r="R167" t="n">
         <v>1</v>
       </c>
+      <c r="S167" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9672,6 +10167,9 @@
       <c r="R168" t="n">
         <v>0</v>
       </c>
+      <c r="S168" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9729,6 +10227,9 @@
       </c>
       <c r="R169" t="n">
         <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -9770,6 +10271,9 @@
       </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9828,6 +10332,9 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9886,6 +10393,9 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9944,6 +10454,9 @@
       <c r="R173" t="n">
         <v>0</v>
       </c>
+      <c r="S173" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10002,6 +10515,9 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
+      <c r="S174" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10060,6 +10576,9 @@
       <c r="R175" t="n">
         <v>0</v>
       </c>
+      <c r="S175" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10118,6 +10637,9 @@
       <c r="R176" t="n">
         <v>1</v>
       </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10176,6 +10698,9 @@
       <c r="R177" t="n">
         <v>1</v>
       </c>
+      <c r="S177" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10234,6 +10759,9 @@
       <c r="R178" t="n">
         <v>0</v>
       </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10292,6 +10820,9 @@
       <c r="R179" t="n">
         <v>2</v>
       </c>
+      <c r="S179" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10350,6 +10881,9 @@
       <c r="R180" t="n">
         <v>0</v>
       </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10408,6 +10942,9 @@
       <c r="R181" t="n">
         <v>0</v>
       </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10466,6 +11003,9 @@
       <c r="R182" t="n">
         <v>0</v>
       </c>
+      <c r="S182" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10524,6 +11064,9 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
+      <c r="S183" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10582,6 +11125,9 @@
       <c r="R184" t="n">
         <v>0</v>
       </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10640,6 +11186,9 @@
       <c r="R185" t="n">
         <v>0</v>
       </c>
+      <c r="S185" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10692,6 +11241,9 @@
       </c>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10750,6 +11302,9 @@
       <c r="R187" t="n">
         <v>5</v>
       </c>
+      <c r="S187" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -10808,6 +11363,9 @@
       <c r="R188" t="n">
         <v>1</v>
       </c>
+      <c r="S188" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -10865,6 +11423,9 @@
       </c>
       <c r="R189" t="n">
         <v>2</v>
+      </c>
+      <c r="S189" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="190">
@@ -10912,6 +11473,9 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -10970,6 +11534,9 @@
       <c r="R191" t="n">
         <v>0</v>
       </c>
+      <c r="S191" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11028,6 +11595,9 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11086,6 +11656,9 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11144,6 +11717,9 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
+      <c r="S194" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11202,6 +11778,9 @@
       <c r="R195" t="n">
         <v>2</v>
       </c>
+      <c r="S195" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11260,6 +11839,9 @@
       <c r="R196" t="n">
         <v>2</v>
       </c>
+      <c r="S196" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11318,6 +11900,9 @@
       <c r="R197" t="n">
         <v>2</v>
       </c>
+      <c r="S197" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11376,6 +11961,9 @@
       <c r="R198" t="n">
         <v>1</v>
       </c>
+      <c r="S198" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11434,6 +12022,9 @@
       <c r="R199" t="n">
         <v>0</v>
       </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11492,6 +12083,9 @@
       <c r="R200" t="n">
         <v>1</v>
       </c>
+      <c r="S200" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -11550,6 +12144,9 @@
       <c r="R201" t="n">
         <v>1</v>
       </c>
+      <c r="S201" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -11608,6 +12205,9 @@
       <c r="R202" t="n">
         <v>0</v>
       </c>
+      <c r="S202" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -11666,6 +12266,9 @@
       <c r="R203" t="n">
         <v>0</v>
       </c>
+      <c r="S203" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -11724,6 +12327,9 @@
       <c r="R204" t="n">
         <v>1</v>
       </c>
+      <c r="S204" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -11782,6 +12388,9 @@
       <c r="R205" t="n">
         <v>0</v>
       </c>
+      <c r="S205" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -11840,6 +12449,9 @@
       <c r="R206" t="n">
         <v>1</v>
       </c>
+      <c r="S206" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -11898,6 +12510,9 @@
       <c r="R207" t="n">
         <v>0</v>
       </c>
+      <c r="S207" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -11955,6 +12570,9 @@
       </c>
       <c r="R208" t="n">
         <v>1</v>
+      </c>
+      <c r="S208" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="209">
@@ -11996,6 +12614,9 @@
       </c>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr"/>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12053,6 +12674,9 @@
       </c>
       <c r="R210" t="n">
         <v>19</v>
+      </c>
+      <c r="S210" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="211">
@@ -12100,6 +12724,9 @@
       <c r="R211" t="n">
         <v>0</v>
       </c>
+      <c r="S211" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12158,6 +12785,9 @@
       <c r="R212" t="n">
         <v>0</v>
       </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12210,6 +12840,9 @@
       </c>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12268,6 +12901,9 @@
       <c r="R214" t="n">
         <v>0</v>
       </c>
+      <c r="S214" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12326,6 +12962,9 @@
       <c r="R215" t="n">
         <v>0</v>
       </c>
+      <c r="S215" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12384,6 +13023,9 @@
       <c r="R216" t="n">
         <v>1</v>
       </c>
+      <c r="S216" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12442,6 +13084,9 @@
       <c r="R217" t="n">
         <v>0</v>
       </c>
+      <c r="S217" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12500,6 +13145,9 @@
       <c r="R218" t="n">
         <v>0</v>
       </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -12558,6 +13206,9 @@
       <c r="R219" t="n">
         <v>1</v>
       </c>
+      <c r="S219" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -12616,6 +13267,9 @@
       <c r="R220" t="n">
         <v>0</v>
       </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -12674,6 +13328,9 @@
       <c r="R221" t="n">
         <v>0</v>
       </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -12732,6 +13389,9 @@
       <c r="R222" t="n">
         <v>1</v>
       </c>
+      <c r="S222" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -12790,6 +13450,9 @@
       <c r="R223" t="n">
         <v>0</v>
       </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -12848,6 +13511,9 @@
       <c r="R224" t="n">
         <v>0</v>
       </c>
+      <c r="S224" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -12900,6 +13566,9 @@
       </c>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -12958,6 +13627,9 @@
       <c r="R226" t="n">
         <v>0</v>
       </c>
+      <c r="S226" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13016,6 +13688,9 @@
       <c r="R227" t="n">
         <v>0</v>
       </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13074,6 +13749,9 @@
       <c r="R228" t="n">
         <v>0</v>
       </c>
+      <c r="S228" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -13132,6 +13810,9 @@
       <c r="R229" t="n">
         <v>0</v>
       </c>
+      <c r="S229" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -13190,6 +13871,9 @@
       <c r="R230" t="n">
         <v>2</v>
       </c>
+      <c r="S230" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -13248,6 +13932,9 @@
       <c r="R231" t="n">
         <v>4</v>
       </c>
+      <c r="S231" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -13305,6 +13992,9 @@
       </c>
       <c r="R232" t="n">
         <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="233">
@@ -13346,6 +14036,9 @@
       </c>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -13398,6 +14091,9 @@
       </c>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
+      <c r="S234" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -13456,6 +14152,9 @@
       <c r="R235" t="n">
         <v>0</v>
       </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -13514,6 +14213,9 @@
       <c r="R236" t="n">
         <v>7</v>
       </c>
+      <c r="S236" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -13571,6 +14273,9 @@
       </c>
       <c r="R237" t="n">
         <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="238">
@@ -13618,6 +14323,9 @@
       <c r="R238" t="n">
         <v>0</v>
       </c>
+      <c r="S238" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -13676,6 +14384,9 @@
       <c r="R239" t="n">
         <v>1</v>
       </c>
+      <c r="S239" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -13734,6 +14445,9 @@
       <c r="R240" t="n">
         <v>0</v>
       </c>
+      <c r="S240" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -13792,6 +14506,9 @@
       <c r="R241" t="n">
         <v>0</v>
       </c>
+      <c r="S241" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -13850,6 +14567,9 @@
       <c r="R242" t="n">
         <v>0</v>
       </c>
+      <c r="S242" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -13908,6 +14628,9 @@
       <c r="R243" t="n">
         <v>0</v>
       </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -13965,6 +14688,9 @@
       </c>
       <c r="R244" t="n">
         <v>1</v>
+      </c>
+      <c r="S244" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="245">
@@ -13994,6 +14720,7 @@
       <c r="P245" t="inlineStr"/>
       <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -14052,6 +14779,9 @@
       <c r="R246" t="n">
         <v>3</v>
       </c>
+      <c r="S246" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -14104,6 +14834,9 @@
       </c>
       <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr"/>
+      <c r="S247" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -14162,6 +14895,9 @@
       <c r="R248" t="n">
         <v>0</v>
       </c>
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -14220,6 +14956,9 @@
       <c r="R249" t="n">
         <v>1</v>
       </c>
+      <c r="S249" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -14278,6 +15017,9 @@
       <c r="R250" t="n">
         <v>1</v>
       </c>
+      <c r="S250" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -14336,6 +15078,9 @@
       <c r="R251" t="n">
         <v>0</v>
       </c>
+      <c r="S251" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -14394,6 +15139,9 @@
       <c r="R252" t="n">
         <v>0</v>
       </c>
+      <c r="S252" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -14451,6 +15199,9 @@
       </c>
       <c r="R253" t="n">
         <v>0</v>
+      </c>
+      <c r="S253" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -14492,6 +15243,9 @@
       </c>
       <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr"/>
+      <c r="S254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -14544,6 +15298,9 @@
       </c>
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr"/>
+      <c r="S255" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -14584,6 +15341,9 @@
       </c>
       <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr"/>
+      <c r="S256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -14642,6 +15402,9 @@
       <c r="R257" t="n">
         <v>1</v>
       </c>
+      <c r="S257" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -14700,6 +15463,9 @@
       <c r="R258" t="n">
         <v>1</v>
       </c>
+      <c r="S258" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -14758,6 +15524,9 @@
       <c r="R259" t="n">
         <v>0</v>
       </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -14815,6 +15584,9 @@
       </c>
       <c r="R260" t="n">
         <v>0</v>
+      </c>
+      <c r="S260" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="261">
@@ -14844,6 +15616,7 @@
       <c r="P261" t="inlineStr"/>
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -14901,6 +15674,9 @@
       </c>
       <c r="R262" t="n">
         <v>1</v>
+      </c>
+      <c r="S262" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="263">
@@ -14948,6 +15724,9 @@
       <c r="R263" t="n">
         <v>1</v>
       </c>
+      <c r="S263" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -15006,6 +15785,9 @@
       <c r="R264" t="n">
         <v>0</v>
       </c>
+      <c r="S264" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -15064,6 +15846,9 @@
       <c r="R265" t="n">
         <v>0</v>
       </c>
+      <c r="S265" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -15122,6 +15907,9 @@
       <c r="R266" t="n">
         <v>1</v>
       </c>
+      <c r="S266" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -15179,6 +15967,9 @@
       </c>
       <c r="R267" t="n">
         <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="268">
@@ -15208,6 +15999,7 @@
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -15266,6 +16058,9 @@
       <c r="R269" t="n">
         <v>0</v>
       </c>
+      <c r="S269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -15324,6 +16119,9 @@
       <c r="R270" t="n">
         <v>0</v>
       </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -15381,6 +16179,9 @@
       </c>
       <c r="R271" t="n">
         <v>0</v>
+      </c>
+      <c r="S271" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="272">
@@ -15410,6 +16211,7 @@
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr"/>
+      <c r="S272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -15468,6 +16270,9 @@
       <c r="R273" t="n">
         <v>0</v>
       </c>
+      <c r="S273" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -15525,6 +16330,9 @@
       </c>
       <c r="R274" t="n">
         <v>1</v>
+      </c>
+      <c r="S274" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="275">
@@ -15572,6 +16380,9 @@
       <c r="R275" t="n">
         <v>0</v>
       </c>
+      <c r="S275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -15630,6 +16441,9 @@
       <c r="R276" t="n">
         <v>1</v>
       </c>
+      <c r="S276" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -15688,6 +16502,9 @@
       <c r="R277" t="n">
         <v>0</v>
       </c>
+      <c r="S277" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -15746,6 +16563,9 @@
       <c r="R278" t="n">
         <v>0</v>
       </c>
+      <c r="S278" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -15804,6 +16624,9 @@
       <c r="R279" t="n">
         <v>0</v>
       </c>
+      <c r="S279" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -15860,6 +16683,9 @@
         <v>17</v>
       </c>
       <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15908,6 +16734,9 @@
       <c r="R281" t="n">
         <v>1</v>
       </c>
+      <c r="S281" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -15966,6 +16795,9 @@
       <c r="R282" t="n">
         <v>0</v>
       </c>
+      <c r="S282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -16023,6 +16855,9 @@
       </c>
       <c r="R283" t="n">
         <v>4</v>
+      </c>
+      <c r="S283" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="284">
@@ -16070,6 +16905,9 @@
       <c r="P284" t="inlineStr"/>
       <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr"/>
+      <c r="S284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -16128,6 +16966,9 @@
       <c r="R285" t="n">
         <v>0</v>
       </c>
+      <c r="S285" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -16186,6 +17027,9 @@
       <c r="R286" t="n">
         <v>0</v>
       </c>
+      <c r="S286" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -16244,6 +17088,9 @@
       <c r="R287" t="n">
         <v>0</v>
       </c>
+      <c r="S287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -16301,6 +17148,9 @@
       </c>
       <c r="R288" t="n">
         <v>6</v>
+      </c>
+      <c r="S288" t="n">
+        <v>416</v>
       </c>
     </row>
     <row r="289">
@@ -16346,6 +17196,9 @@
         <v>1</v>
       </c>
       <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16388,6 +17241,9 @@
       </c>
       <c r="Q290" t="inlineStr"/>
       <c r="R290" t="inlineStr"/>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -16446,6 +17302,9 @@
       <c r="R291" t="n">
         <v>0</v>
       </c>
+      <c r="S291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -16504,6 +17363,9 @@
       <c r="R292" t="n">
         <v>0</v>
       </c>
+      <c r="S292" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -16562,6 +17424,9 @@
       <c r="R293" t="n">
         <v>0</v>
       </c>
+      <c r="S293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -16620,6 +17485,9 @@
       <c r="R294" t="n">
         <v>0</v>
       </c>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -16678,6 +17546,9 @@
       <c r="R295" t="n">
         <v>1</v>
       </c>
+      <c r="S295" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -16735,6 +17606,9 @@
       </c>
       <c r="R296" t="n">
         <v>2</v>
+      </c>
+      <c r="S296" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="297">
@@ -16776,6 +17650,9 @@
       </c>
       <c r="Q297" t="inlineStr"/>
       <c r="R297" t="inlineStr"/>
+      <c r="S297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -16828,6 +17705,9 @@
       </c>
       <c r="Q298" t="inlineStr"/>
       <c r="R298" t="inlineStr"/>
+      <c r="S298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -16886,6 +17766,9 @@
       <c r="R299" t="n">
         <v>0</v>
       </c>
+      <c r="S299" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -16944,6 +17827,9 @@
       <c r="R300" t="n">
         <v>0</v>
       </c>
+      <c r="S300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -17002,6 +17888,9 @@
       <c r="R301" t="n">
         <v>1</v>
       </c>
+      <c r="S301" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -17060,6 +17949,9 @@
       <c r="R302" t="n">
         <v>2</v>
       </c>
+      <c r="S302" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -17118,6 +18010,9 @@
       <c r="R303" t="n">
         <v>0</v>
       </c>
+      <c r="S303" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -17176,6 +18071,9 @@
       <c r="R304" t="n">
         <v>0</v>
       </c>
+      <c r="S304" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -17234,6 +18132,9 @@
       <c r="R305" t="n">
         <v>2</v>
       </c>
+      <c r="S305" t="n">
+        <v>336</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -17292,6 +18193,9 @@
       <c r="R306" t="n">
         <v>0</v>
       </c>
+      <c r="S306" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -17350,6 +18254,9 @@
       <c r="R307" t="n">
         <v>11</v>
       </c>
+      <c r="S307" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -17407,6 +18314,9 @@
       </c>
       <c r="R308" t="n">
         <v>2</v>
+      </c>
+      <c r="S308" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="309">
@@ -17454,6 +18364,9 @@
       <c r="R309" t="n">
         <v>0</v>
       </c>
+      <c r="S309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -17512,6 +18425,9 @@
       <c r="R310" t="n">
         <v>0</v>
       </c>
+      <c r="S310" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -17570,6 +18486,9 @@
       <c r="R311" t="n">
         <v>0</v>
       </c>
+      <c r="S311" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -17628,6 +18547,9 @@
       <c r="R312" t="n">
         <v>0</v>
       </c>
+      <c r="S312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -17686,6 +18608,9 @@
       <c r="R313" t="n">
         <v>0</v>
       </c>
+      <c r="S313" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -17744,6 +18669,9 @@
       <c r="R314" t="n">
         <v>0</v>
       </c>
+      <c r="S314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -17796,6 +18724,9 @@
       </c>
       <c r="Q315" t="inlineStr"/>
       <c r="R315" t="inlineStr"/>
+      <c r="S315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -17848,6 +18779,9 @@
       </c>
       <c r="Q316" t="inlineStr"/>
       <c r="R316" t="inlineStr"/>
+      <c r="S316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -17906,6 +18840,9 @@
       <c r="R317" t="n">
         <v>0</v>
       </c>
+      <c r="S317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -17964,6 +18901,9 @@
       <c r="R318" t="n">
         <v>0</v>
       </c>
+      <c r="S318" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -18022,6 +18962,9 @@
       <c r="R319" t="n">
         <v>0</v>
       </c>
+      <c r="S319" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -18080,6 +19023,9 @@
       <c r="R320" t="n">
         <v>0</v>
       </c>
+      <c r="S320" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -18138,6 +19084,9 @@
       <c r="R321" t="n">
         <v>0</v>
       </c>
+      <c r="S321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -18196,6 +19145,9 @@
       <c r="R322" t="n">
         <v>0</v>
       </c>
+      <c r="S322" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -18254,6 +19206,9 @@
       <c r="R323" t="n">
         <v>0</v>
       </c>
+      <c r="S323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -18312,6 +19267,9 @@
       <c r="R324" t="n">
         <v>0</v>
       </c>
+      <c r="S324" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -18370,6 +19328,9 @@
       <c r="R325" t="n">
         <v>0</v>
       </c>
+      <c r="S325" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -18428,6 +19389,9 @@
       <c r="R326" t="n">
         <v>1</v>
       </c>
+      <c r="S326" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -18486,6 +19450,9 @@
       <c r="R327" t="n">
         <v>0</v>
       </c>
+      <c r="S327" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -18543,6 +19510,9 @@
       </c>
       <c r="R328" t="n">
         <v>0</v>
+      </c>
+      <c r="S328" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="329">
@@ -18590,6 +19560,9 @@
       <c r="R329" t="n">
         <v>0</v>
       </c>
+      <c r="S329" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -18648,6 +19621,9 @@
       <c r="R330" t="n">
         <v>1</v>
       </c>
+      <c r="S330" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -18706,6 +19682,9 @@
       <c r="R331" t="n">
         <v>1</v>
       </c>
+      <c r="S331" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -18764,6 +19743,9 @@
       <c r="R332" t="n">
         <v>1</v>
       </c>
+      <c r="S332" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -18822,6 +19804,9 @@
       <c r="R333" t="n">
         <v>0</v>
       </c>
+      <c r="S333" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -18880,6 +19865,9 @@
       <c r="R334" t="n">
         <v>0</v>
       </c>
+      <c r="S334" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -18938,6 +19926,9 @@
       <c r="R335" t="n">
         <v>0</v>
       </c>
+      <c r="S335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -18996,6 +19987,9 @@
       <c r="R336" t="n">
         <v>0</v>
       </c>
+      <c r="S336" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -19053,6 +20047,9 @@
       </c>
       <c r="R337" t="n">
         <v>1</v>
+      </c>
+      <c r="S337" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="338">
@@ -19094,6 +20091,9 @@
       </c>
       <c r="Q338" t="inlineStr"/>
       <c r="R338" t="inlineStr"/>
+      <c r="S338" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -19152,6 +20152,9 @@
       <c r="R339" t="n">
         <v>1</v>
       </c>
+      <c r="S339" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -19210,6 +20213,9 @@
       <c r="R340" t="n">
         <v>1</v>
       </c>
+      <c r="S340" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -19268,6 +20274,9 @@
       <c r="R341" t="n">
         <v>8</v>
       </c>
+      <c r="S341" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -19326,6 +20335,9 @@
       <c r="R342" t="n">
         <v>0</v>
       </c>
+      <c r="S342" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -19384,6 +20396,9 @@
       <c r="R343" t="n">
         <v>0</v>
       </c>
+      <c r="S343" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -19442,6 +20457,9 @@
       <c r="R344" t="n">
         <v>3</v>
       </c>
+      <c r="S344" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -19500,6 +20518,9 @@
       <c r="R345" t="n">
         <v>1</v>
       </c>
+      <c r="S345" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -19558,6 +20579,9 @@
       <c r="R346" t="n">
         <v>0</v>
       </c>
+      <c r="S346" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -19616,6 +20640,9 @@
       <c r="R347" t="n">
         <v>0</v>
       </c>
+      <c r="S347" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -19674,6 +20701,9 @@
       <c r="R348" t="n">
         <v>0</v>
       </c>
+      <c r="S348" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -19730,6 +20760,9 @@
         <v>1</v>
       </c>
       <c r="R349" t="n">
+        <v>0</v>
+      </c>
+      <c r="S349" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19772,6 +20805,9 @@
       </c>
       <c r="Q350" t="inlineStr"/>
       <c r="R350" t="inlineStr"/>
+      <c r="S350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -19830,6 +20866,9 @@
       <c r="R351" t="n">
         <v>0</v>
       </c>
+      <c r="S351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -19888,6 +20927,9 @@
       <c r="R352" t="n">
         <v>0</v>
       </c>
+      <c r="S352" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -19946,6 +20988,9 @@
       <c r="R353" t="n">
         <v>0</v>
       </c>
+      <c r="S353" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -20004,6 +21049,9 @@
       <c r="R354" t="n">
         <v>1</v>
       </c>
+      <c r="S354" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -20062,6 +21110,9 @@
       <c r="R355" t="n">
         <v>1</v>
       </c>
+      <c r="S355" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -20120,6 +21171,9 @@
       <c r="R356" t="n">
         <v>0</v>
       </c>
+      <c r="S356" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -20178,6 +21232,9 @@
       <c r="R357" t="n">
         <v>0</v>
       </c>
+      <c r="S357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -20236,6 +21293,9 @@
       <c r="R358" t="n">
         <v>1</v>
       </c>
+      <c r="S358" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -20294,6 +21354,9 @@
       <c r="R359" t="n">
         <v>0</v>
       </c>
+      <c r="S359" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -20352,6 +21415,9 @@
       <c r="R360" t="n">
         <v>1</v>
       </c>
+      <c r="S360" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -20410,6 +21476,9 @@
       <c r="R361" t="n">
         <v>2</v>
       </c>
+      <c r="S361" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -20468,6 +21537,9 @@
       <c r="R362" t="n">
         <v>0</v>
       </c>
+      <c r="S362" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -20525,6 +21597,9 @@
       </c>
       <c r="R363" t="n">
         <v>0</v>
+      </c>
+      <c r="S363" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -20566,6 +21641,9 @@
       </c>
       <c r="Q364" t="inlineStr"/>
       <c r="R364" t="inlineStr"/>
+      <c r="S364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -20624,6 +21702,9 @@
       <c r="R365" t="n">
         <v>0</v>
       </c>
+      <c r="S365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -20682,6 +21763,9 @@
       <c r="R366" t="n">
         <v>0</v>
       </c>
+      <c r="S366" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -20740,6 +21824,9 @@
       <c r="R367" t="n">
         <v>0</v>
       </c>
+      <c r="S367" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -20798,6 +21885,9 @@
       <c r="R368" t="n">
         <v>0</v>
       </c>
+      <c r="S368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -20855,6 +21945,9 @@
       </c>
       <c r="R369" t="n">
         <v>0</v>
+      </c>
+      <c r="S369" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -20902,6 +21995,9 @@
       <c r="P370" t="inlineStr"/>
       <c r="Q370" t="inlineStr"/>
       <c r="R370" t="inlineStr"/>
+      <c r="S370" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -20960,6 +22056,9 @@
       <c r="R371" t="n">
         <v>0</v>
       </c>
+      <c r="S371" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -21018,6 +22117,9 @@
       <c r="R372" t="n">
         <v>0</v>
       </c>
+      <c r="S372" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -21076,6 +22178,9 @@
       <c r="R373" t="n">
         <v>1</v>
       </c>
+      <c r="S373" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -21134,6 +22239,9 @@
       <c r="R374" t="n">
         <v>2</v>
       </c>
+      <c r="S374" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -21192,6 +22300,9 @@
       <c r="R375" t="n">
         <v>0</v>
       </c>
+      <c r="S375" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -21250,6 +22361,9 @@
       <c r="R376" t="n">
         <v>0</v>
       </c>
+      <c r="S376" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -21308,6 +22422,9 @@
       <c r="R377" t="n">
         <v>0</v>
       </c>
+      <c r="S377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -21366,6 +22483,9 @@
       <c r="R378" t="n">
         <v>0</v>
       </c>
+      <c r="S378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -21424,6 +22544,9 @@
       <c r="R379" t="n">
         <v>1</v>
       </c>
+      <c r="S379" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -21482,6 +22605,9 @@
       <c r="R380" t="n">
         <v>0</v>
       </c>
+      <c r="S380" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -21540,6 +22666,9 @@
       <c r="R381" t="n">
         <v>1</v>
       </c>
+      <c r="S381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -21598,6 +22727,9 @@
       <c r="R382" t="n">
         <v>0</v>
       </c>
+      <c r="S382" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -21656,6 +22788,9 @@
       <c r="R383" t="n">
         <v>0</v>
       </c>
+      <c r="S383" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -21714,6 +22849,9 @@
       <c r="R384" t="n">
         <v>3</v>
       </c>
+      <c r="S384" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -21772,6 +22910,9 @@
       <c r="R385" t="n">
         <v>3</v>
       </c>
+      <c r="S385" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -21830,6 +22971,9 @@
       <c r="R386" t="n">
         <v>0</v>
       </c>
+      <c r="S386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -21887,6 +23031,9 @@
       </c>
       <c r="R387" t="n">
         <v>0</v>
+      </c>
+      <c r="S387" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="388">
@@ -21934,6 +23081,9 @@
       <c r="R388" t="n">
         <v>1</v>
       </c>
+      <c r="S388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -21992,6 +23142,9 @@
       <c r="R389" t="n">
         <v>0</v>
       </c>
+      <c r="S389" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -22044,6 +23197,9 @@
       <c r="R390" t="n">
         <v>0</v>
       </c>
+      <c r="S390" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -22102,6 +23258,9 @@
       <c r="R391" t="n">
         <v>0</v>
       </c>
+      <c r="S391" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -22160,6 +23319,9 @@
       <c r="R392" t="n">
         <v>1</v>
       </c>
+      <c r="S392" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -22218,6 +23380,9 @@
       <c r="R393" t="n">
         <v>0</v>
       </c>
+      <c r="S393" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -22276,6 +23441,9 @@
       <c r="R394" t="n">
         <v>1</v>
       </c>
+      <c r="S394" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -22334,6 +23502,9 @@
       <c r="R395" t="n">
         <v>0</v>
       </c>
+      <c r="S395" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -22392,6 +23563,9 @@
       <c r="R396" t="n">
         <v>0</v>
       </c>
+      <c r="S396" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -22450,6 +23624,9 @@
       <c r="R397" t="n">
         <v>0</v>
       </c>
+      <c r="S397" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -22508,6 +23685,9 @@
       <c r="R398" t="n">
         <v>0</v>
       </c>
+      <c r="S398" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -22566,6 +23746,9 @@
       <c r="R399" t="n">
         <v>0</v>
       </c>
+      <c r="S399" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -22624,6 +23807,9 @@
       <c r="R400" t="n">
         <v>1</v>
       </c>
+      <c r="S400" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -22682,6 +23868,9 @@
       <c r="R401" t="n">
         <v>1</v>
       </c>
+      <c r="S401" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -22734,6 +23923,9 @@
       </c>
       <c r="Q402" t="inlineStr"/>
       <c r="R402" t="inlineStr"/>
+      <c r="S402" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -22791,6 +23983,9 @@
       </c>
       <c r="R403" t="n">
         <v>0</v>
+      </c>
+      <c r="S403" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -22832,6 +24027,9 @@
       </c>
       <c r="Q404" t="inlineStr"/>
       <c r="R404" t="inlineStr"/>
+      <c r="S404" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -22890,6 +24088,9 @@
       <c r="R405" t="n">
         <v>0</v>
       </c>
+      <c r="S405" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -22948,6 +24149,9 @@
       <c r="R406" t="n">
         <v>0</v>
       </c>
+      <c r="S406" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -23004,6 +24208,9 @@
         <v>5</v>
       </c>
       <c r="R407" t="n">
+        <v>0</v>
+      </c>
+      <c r="S407" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23046,6 +24253,9 @@
       </c>
       <c r="Q408" t="inlineStr"/>
       <c r="R408" t="inlineStr"/>
+      <c r="S408" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -23104,6 +24314,9 @@
       <c r="R409" t="n">
         <v>0</v>
       </c>
+      <c r="S409" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -23162,6 +24375,9 @@
       <c r="R410" t="n">
         <v>3</v>
       </c>
+      <c r="S410" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -23220,6 +24436,9 @@
       <c r="R411" t="n">
         <v>0</v>
       </c>
+      <c r="S411" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -23278,6 +24497,9 @@
       <c r="R412" t="n">
         <v>0</v>
       </c>
+      <c r="S412" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -23336,6 +24558,9 @@
       <c r="R413" t="n">
         <v>0</v>
       </c>
+      <c r="S413" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -23394,6 +24619,9 @@
       <c r="R414" t="n">
         <v>0</v>
       </c>
+      <c r="S414" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -23452,6 +24680,9 @@
       <c r="R415" t="n">
         <v>0</v>
       </c>
+      <c r="S415" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -23510,6 +24741,9 @@
       <c r="R416" t="n">
         <v>0</v>
       </c>
+      <c r="S416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -23568,6 +24802,9 @@
       <c r="R417" t="n">
         <v>1</v>
       </c>
+      <c r="S417" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -23626,6 +24863,9 @@
       <c r="R418" t="n">
         <v>2</v>
       </c>
+      <c r="S418" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -23684,6 +24924,9 @@
       <c r="R419" t="n">
         <v>1</v>
       </c>
+      <c r="S419" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -23736,6 +24979,9 @@
       </c>
       <c r="Q420" t="inlineStr"/>
       <c r="R420" t="inlineStr"/>
+      <c r="S420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -23764,6 +25010,7 @@
       <c r="P421" t="inlineStr"/>
       <c r="Q421" t="inlineStr"/>
       <c r="R421" t="inlineStr"/>
+      <c r="S421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -23822,6 +25069,9 @@
       <c r="R422" t="n">
         <v>12</v>
       </c>
+      <c r="S422" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -23880,6 +25130,9 @@
       <c r="R423" t="n">
         <v>1</v>
       </c>
+      <c r="S423" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -23936,6 +25189,9 @@
         <v>2</v>
       </c>
       <c r="R424" t="n">
+        <v>0</v>
+      </c>
+      <c r="S424" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23978,6 +25234,9 @@
       </c>
       <c r="Q425" t="inlineStr"/>
       <c r="R425" t="inlineStr"/>
+      <c r="S425" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -24034,6 +25293,9 @@
         <v>30</v>
       </c>
       <c r="R426" t="n">
+        <v>2</v>
+      </c>
+      <c r="S426" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24082,6 +25344,9 @@
       <c r="R427" t="n">
         <v>0</v>
       </c>
+      <c r="S427" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -24140,6 +25405,9 @@
       <c r="R428" t="n">
         <v>1</v>
       </c>
+      <c r="S428" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -24198,6 +25466,9 @@
       <c r="R429" t="n">
         <v>6</v>
       </c>
+      <c r="S429" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -24256,6 +25527,9 @@
       <c r="R430" t="n">
         <v>0</v>
       </c>
+      <c r="S430" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -24314,6 +25588,9 @@
       <c r="R431" t="n">
         <v>0</v>
       </c>
+      <c r="S431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -24370,6 +25647,9 @@
         <v>1</v>
       </c>
       <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24412,6 +25692,9 @@
       </c>
       <c r="Q433" t="inlineStr"/>
       <c r="R433" t="inlineStr"/>
+      <c r="S433" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -24470,6 +25753,9 @@
       <c r="R434" t="n">
         <v>0</v>
       </c>
+      <c r="S434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -24528,6 +25814,9 @@
       <c r="R435" t="n">
         <v>3</v>
       </c>
+      <c r="S435" t="n">
+        <v>237</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -24586,6 +25875,9 @@
       <c r="R436" t="n">
         <v>0</v>
       </c>
+      <c r="S436" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -24644,6 +25936,9 @@
       <c r="R437" t="n">
         <v>0</v>
       </c>
+      <c r="S437" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -24702,6 +25997,9 @@
       <c r="R438" t="n">
         <v>0</v>
       </c>
+      <c r="S438" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -24760,6 +26058,9 @@
       <c r="R439" t="n">
         <v>0</v>
       </c>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -24818,6 +26119,9 @@
       <c r="R440" t="n">
         <v>0</v>
       </c>
+      <c r="S440" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -24876,6 +26180,9 @@
       <c r="R441" t="n">
         <v>1</v>
       </c>
+      <c r="S441" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -24934,6 +26241,9 @@
       <c r="R442" t="n">
         <v>0</v>
       </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -24992,6 +26302,9 @@
       <c r="R443" t="n">
         <v>0</v>
       </c>
+      <c r="S443" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -25049,6 +26362,9 @@
       </c>
       <c r="R444" t="n">
         <v>0</v>
+      </c>
+      <c r="S444" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="445">
@@ -25096,6 +26412,9 @@
       <c r="R445" t="n">
         <v>0</v>
       </c>
+      <c r="S445" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -25136,6 +26455,9 @@
       </c>
       <c r="Q446" t="inlineStr"/>
       <c r="R446" t="inlineStr"/>
+      <c r="S446" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -25194,6 +26516,9 @@
       <c r="R447" t="n">
         <v>0</v>
       </c>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -25252,6 +26577,9 @@
       <c r="R448" t="n">
         <v>0</v>
       </c>
+      <c r="S448" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -25310,6 +26638,9 @@
       <c r="R449" t="n">
         <v>0</v>
       </c>
+      <c r="S449" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -25368,6 +26699,9 @@
       <c r="R450" t="n">
         <v>3</v>
       </c>
+      <c r="S450" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -25426,6 +26760,9 @@
       <c r="R451" t="n">
         <v>1</v>
       </c>
+      <c r="S451" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -25484,6 +26821,9 @@
       <c r="R452" t="n">
         <v>0</v>
       </c>
+      <c r="S452" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -25542,6 +26882,9 @@
       <c r="R453" t="n">
         <v>0</v>
       </c>
+      <c r="S453" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -25600,6 +26943,9 @@
       <c r="R454" t="n">
         <v>0</v>
       </c>
+      <c r="S454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -25658,6 +27004,9 @@
       <c r="R455" t="n">
         <v>0</v>
       </c>
+      <c r="S455" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -25716,6 +27065,9 @@
       <c r="R456" t="n">
         <v>0</v>
       </c>
+      <c r="S456" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -25774,6 +27126,9 @@
       <c r="R457" t="n">
         <v>3</v>
       </c>
+      <c r="S457" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -25831,6 +27186,9 @@
       </c>
       <c r="R458" t="n">
         <v>0</v>
+      </c>
+      <c r="S458" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="459">
@@ -25878,6 +27236,9 @@
       <c r="R459" t="n">
         <v>0</v>
       </c>
+      <c r="S459" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -25936,6 +27297,9 @@
       <c r="R460" t="n">
         <v>0</v>
       </c>
+      <c r="S460" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -25994,6 +27358,9 @@
       <c r="R461" t="n">
         <v>0</v>
       </c>
+      <c r="S461" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -26052,6 +27419,9 @@
       <c r="R462" t="n">
         <v>0</v>
       </c>
+      <c r="S462" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -26110,6 +27480,9 @@
       <c r="R463" t="n">
         <v>0</v>
       </c>
+      <c r="S463" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -26168,6 +27541,9 @@
       <c r="R464" t="n">
         <v>0</v>
       </c>
+      <c r="S464" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -26226,6 +27602,9 @@
       <c r="R465" t="n">
         <v>1</v>
       </c>
+      <c r="S465" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -26284,6 +27663,9 @@
       <c r="R466" t="n">
         <v>3</v>
       </c>
+      <c r="S466" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -26342,6 +27724,9 @@
       <c r="R467" t="n">
         <v>5</v>
       </c>
+      <c r="S467" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -26399,6 +27784,9 @@
       </c>
       <c r="R468" t="n">
         <v>1</v>
+      </c>
+      <c r="S468" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="469">
@@ -26446,6 +27834,9 @@
       <c r="R469" t="n">
         <v>0</v>
       </c>
+      <c r="S469" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -26504,6 +27895,9 @@
       <c r="R470" t="n">
         <v>0</v>
       </c>
+      <c r="S470" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -26562,6 +27956,9 @@
       <c r="R471" t="n">
         <v>0</v>
       </c>
+      <c r="S471" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -26620,6 +28017,9 @@
       <c r="R472" t="n">
         <v>1</v>
       </c>
+      <c r="S472" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -26678,6 +28078,9 @@
       <c r="R473" t="n">
         <v>0</v>
       </c>
+      <c r="S473" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -26736,6 +28139,9 @@
       <c r="R474" t="n">
         <v>0</v>
       </c>
+      <c r="S474" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -26793,6 +28199,9 @@
       </c>
       <c r="R475" t="n">
         <v>0</v>
+      </c>
+      <c r="S475" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="476">
@@ -26840,6 +28249,9 @@
       <c r="R476" t="n">
         <v>0</v>
       </c>
+      <c r="S476" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -26892,6 +28304,9 @@
       <c r="R477" t="n">
         <v>1</v>
       </c>
+      <c r="S477" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -26950,6 +28365,9 @@
       <c r="R478" t="n">
         <v>1</v>
       </c>
+      <c r="S478" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -27002,6 +28420,9 @@
       <c r="R479" t="n">
         <v>0</v>
       </c>
+      <c r="S479" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -27058,6 +28479,9 @@
         <v>1</v>
       </c>
       <c r="R480" t="n">
+        <v>0</v>
+      </c>
+      <c r="S480" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27100,6 +28524,9 @@
       </c>
       <c r="Q481" t="inlineStr"/>
       <c r="R481" t="inlineStr"/>
+      <c r="S481" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -27158,6 +28585,9 @@
       <c r="R482" t="n">
         <v>0</v>
       </c>
+      <c r="S482" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -27210,6 +28640,9 @@
       </c>
       <c r="Q483" t="inlineStr"/>
       <c r="R483" t="inlineStr"/>
+      <c r="S483" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -27267,6 +28700,9 @@
       </c>
       <c r="R484" t="n">
         <v>0</v>
+      </c>
+      <c r="S484" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="485">
@@ -27312,6 +28748,9 @@
         <v>4</v>
       </c>
       <c r="R485" t="n">
+        <v>0</v>
+      </c>
+      <c r="S485" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27354,6 +28793,9 @@
       <c r="R486" t="n">
         <v>0</v>
       </c>
+      <c r="S486" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -27394,6 +28836,9 @@
       </c>
       <c r="Q487" t="inlineStr"/>
       <c r="R487" t="inlineStr"/>
+      <c r="S487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -27434,6 +28879,9 @@
       </c>
       <c r="Q488" t="inlineStr"/>
       <c r="R488" t="inlineStr"/>
+      <c r="S488" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -27491,6 +28939,9 @@
       </c>
       <c r="R489" t="n">
         <v>10</v>
+      </c>
+      <c r="S489" t="n">
+        <v>760</v>
       </c>
     </row>
     <row r="490">
@@ -27520,6 +28971,7 @@
       <c r="P490" t="inlineStr"/>
       <c r="Q490" t="inlineStr"/>
       <c r="R490" t="inlineStr"/>
+      <c r="S490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -27578,6 +29030,9 @@
       <c r="R491" t="n">
         <v>0</v>
       </c>
+      <c r="S491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -27636,6 +29091,9 @@
       <c r="R492" t="n">
         <v>0</v>
       </c>
+      <c r="S492" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -27694,6 +29152,9 @@
       <c r="R493" t="n">
         <v>0</v>
       </c>
+      <c r="S493" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -27752,6 +29213,9 @@
       <c r="R494" t="n">
         <v>0</v>
       </c>
+      <c r="S494" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -27810,6 +29274,9 @@
       <c r="R495" t="n">
         <v>0</v>
       </c>
+      <c r="S495" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -27856,6 +29323,9 @@
       </c>
       <c r="Q496" t="inlineStr"/>
       <c r="R496" t="inlineStr"/>
+      <c r="S496" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -27914,6 +29384,9 @@
       <c r="R497" t="n">
         <v>1</v>
       </c>
+      <c r="S497" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -27972,6 +29445,9 @@
       <c r="R498" t="n">
         <v>1</v>
       </c>
+      <c r="S498" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -28030,6 +29506,9 @@
       <c r="R499" t="n">
         <v>1</v>
       </c>
+      <c r="S499" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -28088,6 +29567,9 @@
       <c r="R500" t="n">
         <v>0</v>
       </c>
+      <c r="S500" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -28146,6 +29628,9 @@
       <c r="R501" t="n">
         <v>1</v>
       </c>
+      <c r="S501" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -28204,6 +29689,9 @@
       <c r="R502" t="n">
         <v>0</v>
       </c>
+      <c r="S502" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -28262,6 +29750,9 @@
       <c r="R503" t="n">
         <v>0</v>
       </c>
+      <c r="S503" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -28320,6 +29811,9 @@
       <c r="R504" t="n">
         <v>0</v>
       </c>
+      <c r="S504" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -28372,6 +29866,9 @@
       </c>
       <c r="Q505" t="inlineStr"/>
       <c r="R505" t="inlineStr"/>
+      <c r="S505" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -28412,6 +29909,9 @@
       </c>
       <c r="Q506" t="inlineStr"/>
       <c r="R506" t="inlineStr"/>
+      <c r="S506" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -28470,6 +29970,9 @@
       <c r="R507" t="n">
         <v>0</v>
       </c>
+      <c r="S507" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -28528,6 +30031,9 @@
       <c r="R508" t="n">
         <v>0</v>
       </c>
+      <c r="S508" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -28586,6 +30092,9 @@
       <c r="R509" t="n">
         <v>0</v>
       </c>
+      <c r="S509" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -28644,6 +30153,9 @@
       <c r="R510" t="n">
         <v>0</v>
       </c>
+      <c r="S510" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -28702,6 +30214,9 @@
       <c r="R511" t="n">
         <v>0</v>
       </c>
+      <c r="S511" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -28760,6 +30275,9 @@
       <c r="R512" t="n">
         <v>0</v>
       </c>
+      <c r="S512" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -28818,6 +30336,9 @@
       <c r="R513" t="n">
         <v>0</v>
       </c>
+      <c r="S513" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -28876,6 +30397,9 @@
       <c r="R514" t="n">
         <v>0</v>
       </c>
+      <c r="S514" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -28933,6 +30457,9 @@
       </c>
       <c r="R515" t="n">
         <v>0</v>
+      </c>
+      <c r="S515" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="516">
@@ -28980,6 +30507,9 @@
       <c r="R516" t="n">
         <v>0</v>
       </c>
+      <c r="S516" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -29037,6 +30567,9 @@
       </c>
       <c r="R517" t="n">
         <v>0</v>
+      </c>
+      <c r="S517" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="518">
@@ -29084,6 +30617,9 @@
       <c r="R518" t="n">
         <v>0</v>
       </c>
+      <c r="S518" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -29130,6 +30666,9 @@
       <c r="R519" t="n">
         <v>0</v>
       </c>
+      <c r="S519" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -29188,6 +30727,9 @@
       <c r="R520" t="n">
         <v>0</v>
       </c>
+      <c r="S520" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -29246,6 +30788,9 @@
       <c r="R521" t="n">
         <v>3</v>
       </c>
+      <c r="S521" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -29304,6 +30849,9 @@
       <c r="R522" t="n">
         <v>0</v>
       </c>
+      <c r="S522" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -29362,6 +30910,9 @@
       <c r="R523" t="n">
         <v>1</v>
       </c>
+      <c r="S523" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -29418,6 +30969,9 @@
         <v>9</v>
       </c>
       <c r="R524" t="n">
+        <v>0</v>
+      </c>
+      <c r="S524" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29460,6 +31014,9 @@
       </c>
       <c r="Q525" t="inlineStr"/>
       <c r="R525" t="inlineStr"/>
+      <c r="S525" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -29518,6 +31075,9 @@
       <c r="R526" t="n">
         <v>1</v>
       </c>
+      <c r="S526" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -29576,6 +31136,9 @@
       <c r="R527" t="n">
         <v>0</v>
       </c>
+      <c r="S527" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -29634,6 +31197,9 @@
       <c r="R528" t="n">
         <v>0</v>
       </c>
+      <c r="S528" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -29692,6 +31258,9 @@
       <c r="R529" t="n">
         <v>0</v>
       </c>
+      <c r="S529" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -29750,6 +31319,9 @@
       <c r="R530" t="n">
         <v>0</v>
       </c>
+      <c r="S530" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -29808,6 +31380,9 @@
       <c r="R531" t="n">
         <v>0</v>
       </c>
+      <c r="S531" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -29866,6 +31441,9 @@
       <c r="R532" t="n">
         <v>0</v>
       </c>
+      <c r="S532" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -29924,6 +31502,9 @@
       <c r="R533" t="n">
         <v>0</v>
       </c>
+      <c r="S533" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -29982,6 +31563,9 @@
       <c r="R534" t="n">
         <v>0</v>
       </c>
+      <c r="S534" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -30040,6 +31624,9 @@
       <c r="R535" t="n">
         <v>3</v>
       </c>
+      <c r="S535" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -30098,6 +31685,9 @@
       <c r="R536" t="n">
         <v>0</v>
       </c>
+      <c r="S536" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -30156,6 +31746,9 @@
       <c r="R537" t="n">
         <v>0</v>
       </c>
+      <c r="S537" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -30214,6 +31807,9 @@
       <c r="R538" t="n">
         <v>0</v>
       </c>
+      <c r="S538" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -30271,6 +31867,9 @@
       </c>
       <c r="R539" t="n">
         <v>3</v>
+      </c>
+      <c r="S539" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="540">
@@ -30317,6 +31916,9 @@
       </c>
       <c r="R540" t="n">
         <v>1</v>
+      </c>
+      <c r="S540" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="541">
@@ -30358,6 +31960,9 @@
       <c r="R541" t="n">
         <v>0</v>
       </c>
+      <c r="S541" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -30410,6 +32015,9 @@
       </c>
       <c r="Q542" t="inlineStr"/>
       <c r="R542" t="inlineStr"/>
+      <c r="S542" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -30466,6 +32074,9 @@
         <v>1</v>
       </c>
       <c r="R543" t="n">
+        <v>0</v>
+      </c>
+      <c r="S543" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30508,6 +32119,9 @@
       </c>
       <c r="Q544" t="inlineStr"/>
       <c r="R544" t="inlineStr"/>
+      <c r="S544" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -30554,6 +32168,9 @@
       <c r="R545" t="n">
         <v>0</v>
       </c>
+      <c r="S545" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -30611,6 +32228,9 @@
       </c>
       <c r="R546" t="n">
         <v>0</v>
+      </c>
+      <c r="S546" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="547">
@@ -30658,6 +32278,9 @@
       <c r="R547" t="n">
         <v>0</v>
       </c>
+      <c r="S547" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -30716,6 +32339,9 @@
       <c r="R548" t="n">
         <v>0</v>
       </c>
+      <c r="S548" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -30768,6 +32394,9 @@
       <c r="R549" t="n">
         <v>1</v>
       </c>
+      <c r="S549" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -30826,6 +32455,9 @@
       <c r="R550" t="n">
         <v>0</v>
       </c>
+      <c r="S550" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -30884,6 +32516,9 @@
       <c r="R551" t="n">
         <v>1</v>
       </c>
+      <c r="S551" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -30942,6 +32577,9 @@
       <c r="R552" t="n">
         <v>0</v>
       </c>
+      <c r="S552" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -31000,6 +32638,9 @@
       <c r="R553" t="n">
         <v>0</v>
       </c>
+      <c r="S553" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -31058,6 +32699,9 @@
       <c r="R554" t="n">
         <v>1</v>
       </c>
+      <c r="S554" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -31110,6 +32754,9 @@
       </c>
       <c r="Q555" t="inlineStr"/>
       <c r="R555" t="inlineStr"/>
+      <c r="S555" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -31156,6 +32803,9 @@
       <c r="R556" t="n">
         <v>0</v>
       </c>
+      <c r="S556" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -31214,6 +32864,9 @@
       <c r="R557" t="n">
         <v>2</v>
       </c>
+      <c r="S557" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -31272,6 +32925,9 @@
       <c r="R558" t="n">
         <v>3</v>
       </c>
+      <c r="S558" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -31329,6 +32985,9 @@
       </c>
       <c r="R559" t="n">
         <v>5</v>
+      </c>
+      <c r="S559" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="560">
@@ -31376,6 +33035,9 @@
       <c r="R560" t="n">
         <v>0</v>
       </c>
+      <c r="S560" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -31434,6 +33096,9 @@
       <c r="R561" t="n">
         <v>0</v>
       </c>
+      <c r="S561" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -31492,6 +33157,9 @@
       <c r="R562" t="n">
         <v>0</v>
       </c>
+      <c r="S562" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -31550,6 +33218,9 @@
       <c r="R563" t="n">
         <v>0</v>
       </c>
+      <c r="S563" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -31608,6 +33279,9 @@
       <c r="R564" t="n">
         <v>2</v>
       </c>
+      <c r="S564" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -31666,6 +33340,9 @@
       <c r="R565" t="n">
         <v>0</v>
       </c>
+      <c r="S565" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -31718,6 +33395,9 @@
       <c r="R566" t="n">
         <v>0</v>
       </c>
+      <c r="S566" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -31776,6 +33456,9 @@
       <c r="R567" t="n">
         <v>0</v>
       </c>
+      <c r="S567" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -31834,6 +33517,9 @@
       <c r="R568" t="n">
         <v>0</v>
       </c>
+      <c r="S568" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -31892,6 +33578,9 @@
       <c r="R569" t="n">
         <v>0</v>
       </c>
+      <c r="S569" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -31944,6 +33633,9 @@
       </c>
       <c r="Q570" t="inlineStr"/>
       <c r="R570" t="inlineStr"/>
+      <c r="S570" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -31984,6 +33676,9 @@
       </c>
       <c r="Q571" t="inlineStr"/>
       <c r="R571" t="inlineStr"/>
+      <c r="S571" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -32030,6 +33725,9 @@
       <c r="R572" t="n">
         <v>0</v>
       </c>
+      <c r="S572" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -32070,6 +33768,9 @@
       </c>
       <c r="Q573" t="inlineStr"/>
       <c r="R573" t="inlineStr"/>
+      <c r="S573" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -32128,6 +33829,9 @@
       <c r="R574" t="n">
         <v>0</v>
       </c>
+      <c r="S574" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -32186,6 +33890,9 @@
       <c r="R575" t="n">
         <v>0</v>
       </c>
+      <c r="S575" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -32238,6 +33945,9 @@
       </c>
       <c r="Q576" t="inlineStr"/>
       <c r="R576" t="inlineStr"/>
+      <c r="S576" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -32296,6 +34006,9 @@
       <c r="R577" t="n">
         <v>0</v>
       </c>
+      <c r="S577" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -32353,6 +34066,9 @@
       </c>
       <c r="R578" t="n">
         <v>0</v>
+      </c>
+      <c r="S578" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="579">
@@ -32394,6 +34110,9 @@
       </c>
       <c r="Q579" t="inlineStr"/>
       <c r="R579" t="inlineStr"/>
+      <c r="S579" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -32452,6 +34171,9 @@
       <c r="R580" t="n">
         <v>0</v>
       </c>
+      <c r="S580" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -32510,6 +34232,9 @@
       <c r="R581" t="n">
         <v>0</v>
       </c>
+      <c r="S581" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -32568,6 +34293,9 @@
       <c r="R582" t="n">
         <v>3</v>
       </c>
+      <c r="S582" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -32626,6 +34354,9 @@
       <c r="R583" t="n">
         <v>4</v>
       </c>
+      <c r="S583" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -32684,6 +34415,9 @@
       <c r="R584" t="n">
         <v>1</v>
       </c>
+      <c r="S584" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -32742,6 +34476,9 @@
       <c r="R585" t="n">
         <v>0</v>
       </c>
+      <c r="S585" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -32800,6 +34537,9 @@
       <c r="R586" t="n">
         <v>0</v>
       </c>
+      <c r="S586" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -32858,6 +34598,9 @@
       <c r="R587" t="n">
         <v>1</v>
       </c>
+      <c r="S587" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -32916,6 +34659,9 @@
       <c r="R588" t="n">
         <v>0</v>
       </c>
+      <c r="S588" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -32974,6 +34720,9 @@
       <c r="R589" t="n">
         <v>0</v>
       </c>
+      <c r="S589" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -33031,6 +34780,9 @@
       </c>
       <c r="R590" t="n">
         <v>0</v>
+      </c>
+      <c r="S590" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="591">
@@ -33078,6 +34830,9 @@
       <c r="R591" t="n">
         <v>0</v>
       </c>
+      <c r="S591" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -33124,6 +34879,9 @@
       <c r="R592" t="n">
         <v>1</v>
       </c>
+      <c r="S592" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -33182,6 +34940,9 @@
       <c r="R593" t="n">
         <v>0</v>
       </c>
+      <c r="S593" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -33240,6 +35001,9 @@
       <c r="R594" t="n">
         <v>0</v>
       </c>
+      <c r="S594" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -33298,6 +35062,9 @@
       <c r="R595" t="n">
         <v>0</v>
       </c>
+      <c r="S595" t="n">
+        <v>204</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -33355,6 +35122,9 @@
       </c>
       <c r="R596" t="n">
         <v>2</v>
+      </c>
+      <c r="S596" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="597">
@@ -33396,6 +35166,9 @@
       </c>
       <c r="Q597" t="inlineStr"/>
       <c r="R597" t="inlineStr"/>
+      <c r="S597" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -33454,6 +35227,9 @@
       <c r="R598" t="n">
         <v>6</v>
       </c>
+      <c r="S598" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -33512,6 +35288,9 @@
       <c r="R599" t="n">
         <v>0</v>
       </c>
+      <c r="S599" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -33569,6 +35348,9 @@
       </c>
       <c r="R600" t="n">
         <v>6</v>
+      </c>
+      <c r="S600" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="601">
@@ -33610,6 +35392,9 @@
       </c>
       <c r="Q601" t="inlineStr"/>
       <c r="R601" t="inlineStr"/>
+      <c r="S601" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -33656,6 +35441,9 @@
       <c r="P602" t="inlineStr"/>
       <c r="Q602" t="inlineStr"/>
       <c r="R602" t="inlineStr"/>
+      <c r="S602" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -33713,6 +35501,9 @@
       </c>
       <c r="R603" t="n">
         <v>0</v>
+      </c>
+      <c r="S603" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -33760,6 +35551,9 @@
       <c r="R604" t="n">
         <v>0</v>
       </c>
+      <c r="S604" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -33818,6 +35612,9 @@
       <c r="R605" t="n">
         <v>1</v>
       </c>
+      <c r="S605" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -33876,6 +35673,9 @@
       <c r="R606" t="n">
         <v>4</v>
       </c>
+      <c r="S606" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -33934,6 +35734,9 @@
       <c r="R607" t="n">
         <v>0</v>
       </c>
+      <c r="S607" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -33992,6 +35795,9 @@
       <c r="R608" t="n">
         <v>1</v>
       </c>
+      <c r="S608" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -34044,6 +35850,9 @@
       </c>
       <c r="Q609" t="inlineStr"/>
       <c r="R609" t="inlineStr"/>
+      <c r="S609" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -34102,6 +35911,9 @@
       <c r="R610" t="n">
         <v>0</v>
       </c>
+      <c r="S610" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -34158,6 +35970,9 @@
         <v>2</v>
       </c>
       <c r="R611" t="n">
+        <v>0</v>
+      </c>
+      <c r="S611" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34206,6 +36021,9 @@
       <c r="R612" t="n">
         <v>0</v>
       </c>
+      <c r="S612" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -34264,6 +36082,9 @@
       <c r="R613" t="n">
         <v>0</v>
       </c>
+      <c r="S613" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -34322,6 +36143,9 @@
       <c r="R614" t="n">
         <v>0</v>
       </c>
+      <c r="S614" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -34380,6 +36204,9 @@
       <c r="R615" t="n">
         <v>0</v>
       </c>
+      <c r="S615" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -34438,6 +36265,9 @@
       <c r="R616" t="n">
         <v>0</v>
       </c>
+      <c r="S616" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -34496,6 +36326,9 @@
       <c r="R617" t="n">
         <v>0</v>
       </c>
+      <c r="S617" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -34554,6 +36387,9 @@
       <c r="R618" t="n">
         <v>3</v>
       </c>
+      <c r="S618" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -34612,6 +36448,9 @@
       <c r="R619" t="n">
         <v>1</v>
       </c>
+      <c r="S619" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -34670,6 +36509,9 @@
       <c r="R620" t="n">
         <v>0</v>
       </c>
+      <c r="S620" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -34728,6 +36570,9 @@
       <c r="R621" t="n">
         <v>0</v>
       </c>
+      <c r="S621" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -34786,6 +36631,9 @@
       <c r="R622" t="n">
         <v>0</v>
       </c>
+      <c r="S622" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -34844,6 +36692,9 @@
       <c r="R623" t="n">
         <v>1</v>
       </c>
+      <c r="S623" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -34902,6 +36753,9 @@
       <c r="R624" t="n">
         <v>0</v>
       </c>
+      <c r="S624" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -34959,6 +36813,9 @@
       </c>
       <c r="R625" t="n">
         <v>0</v>
+      </c>
+      <c r="S625" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="626">
@@ -35006,6 +36863,9 @@
       <c r="R626" t="n">
         <v>0</v>
       </c>
+      <c r="S626" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -35063,6 +36923,9 @@
       </c>
       <c r="R627" t="n">
         <v>0</v>
+      </c>
+      <c r="S627" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="628">
@@ -35110,6 +36973,9 @@
       <c r="R628" t="n">
         <v>0</v>
       </c>
+      <c r="S628" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -35168,6 +37034,9 @@
       <c r="R629" t="n">
         <v>1</v>
       </c>
+      <c r="S629" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -35226,6 +37095,9 @@
       <c r="R630" t="n">
         <v>0</v>
       </c>
+      <c r="S630" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -35284,6 +37156,9 @@
       <c r="R631" t="n">
         <v>0</v>
       </c>
+      <c r="S631" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -35342,6 +37217,9 @@
       <c r="R632" t="n">
         <v>2</v>
       </c>
+      <c r="S632" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -35400,6 +37278,9 @@
       <c r="R633" t="n">
         <v>0</v>
       </c>
+      <c r="S633" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -35457,6 +37338,9 @@
       </c>
       <c r="R634" t="n">
         <v>1</v>
+      </c>
+      <c r="S634" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="635">
@@ -35498,6 +37382,9 @@
       </c>
       <c r="Q635" t="inlineStr"/>
       <c r="R635" t="inlineStr"/>
+      <c r="S635" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -35556,6 +37443,9 @@
       <c r="R636" t="n">
         <v>0</v>
       </c>
+      <c r="S636" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -35614,6 +37504,9 @@
       <c r="R637" t="n">
         <v>0</v>
       </c>
+      <c r="S637" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -35672,6 +37565,9 @@
       <c r="R638" t="n">
         <v>0</v>
       </c>
+      <c r="S638" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -35730,6 +37626,9 @@
       <c r="R639" t="n">
         <v>0</v>
       </c>
+      <c r="S639" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -35788,6 +37687,9 @@
       <c r="R640" t="n">
         <v>0</v>
       </c>
+      <c r="S640" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -35846,6 +37748,9 @@
       <c r="R641" t="n">
         <v>0</v>
       </c>
+      <c r="S641" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -35904,6 +37809,9 @@
       <c r="R642" t="n">
         <v>0</v>
       </c>
+      <c r="S642" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -35962,6 +37870,9 @@
       <c r="R643" t="n">
         <v>0</v>
       </c>
+      <c r="S643" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -36020,6 +37931,9 @@
       <c r="R644" t="n">
         <v>0</v>
       </c>
+      <c r="S644" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -36078,6 +37992,9 @@
       <c r="R645" t="n">
         <v>0</v>
       </c>
+      <c r="S645" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -36134,6 +38051,9 @@
         <v>9</v>
       </c>
       <c r="R646" t="n">
+        <v>0</v>
+      </c>
+      <c r="S646" t="n">
         <v>0</v>
       </c>
     </row>
